--- a/estadisticas/arch/dtrp12.xlsx
+++ b/estadisticas/arch/dtrp12.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DEIMONT\Documents\2021\super\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATOS-EXT/proyectos/Gestor documental Universidad Militar/ArgoUMNG/src/2/estadisticas/arch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE1436C-FB5A-4813-A3E6-307315CB41CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D84A93-DEBF-FA42-B04F-3F4B3AD3C814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15990" xr2:uid="{DCCD86FB-7485-4760-AE19-9F57E802B0C3}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="16000" xr2:uid="{DCCD86FB-7485-4760-AE19-9F57E802B0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Glosario" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1093,13 +1093,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1130,18 +1129,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1150,6 +1137,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1219,61 +1218,44 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>66674</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>800099</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>46421</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1538926</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1" descr="Logo SuperArgo">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A06FBCA-1677-4A40-973B-5B132D2DC693}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D16FAB35-EEE4-694C-8BB4-3118BC173FBE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="476249" y="9525"/>
-          <a:ext cx="4257675" cy="1103696"/>
+          <a:off x="2540000" y="139700"/>
+          <a:ext cx="738826" cy="723900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1282,9 +1264,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1322,7 +1304,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1428,7 +1410,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1570,7 +1552,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1578,141 +1560,141 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B63DF49-11A9-4999-8E10-DB6A1A62160F}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:P6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" customWidth="1"/>
-    <col min="7" max="7" width="24.42578125" customWidth="1"/>
-    <col min="14" max="14" width="19.28515625" customWidth="1"/>
-    <col min="15" max="15" width="27.28515625" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="6" max="6" width="23.33203125" customWidth="1"/>
+    <col min="7" max="7" width="24.5" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" customWidth="1"/>
+    <col min="15" max="15" width="27.33203125" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="22" t="s">
+    <row r="1" spans="2:16" ht="24" x14ac:dyDescent="0.3">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-    </row>
-    <row r="2" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="8" t="s">
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+    </row>
+    <row r="2" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="20"/>
-      <c r="L2" s="18" t="s">
+      <c r="K2" s="22"/>
+      <c r="L2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="18"/>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="9" t="s">
+      <c r="M2" s="20"/>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="21" t="s">
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="18" t="s">
+      <c r="K3" s="23"/>
+      <c r="L3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="18"/>
-    </row>
-    <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-    </row>
-    <row r="5" spans="2:16" ht="21" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="M3" s="20"/>
+    </row>
+    <row r="4" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+    </row>
+    <row r="5" spans="2:16" ht="24" x14ac:dyDescent="0.2">
+      <c r="B5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N5" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1778,279 +1760,279 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFCF6C93-BB54-4676-9E76-524BA0D40F10}">
   <dimension ref="A1:B34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="81.5703125" customWidth="1"/>
+    <col min="1" max="1" width="40.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="14" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="14" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="14" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="14" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="14" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="14" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="14" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="14" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="14" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="14" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="14" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="14" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="14" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="14" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="14" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="16" t="s">
+    <row r="34" spans="1:2" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="16" t="s">
         <v>106</v>
       </c>
     </row>
